--- a/artfynd/A 59078-2025 artfynd.xlsx
+++ b/artfynd/A 59078-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132325751</v>
+        <v>132325802</v>
       </c>
       <c r="B2" t="n">
-        <v>57145</v>
+        <v>79130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529295</v>
+        <v>529767</v>
       </c>
       <c r="R2" t="n">
-        <v>6869696</v>
+        <v>6869908</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Milad Avalinejad Bandari, Julia Svensson</t>
+          <t>Milad Avalinejad Bandari, Alexander Schäpers</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132325802</v>
+        <v>132325751</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>57162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529767</v>
+        <v>529295</v>
       </c>
       <c r="R3" t="n">
-        <v>6869908</v>
+        <v>6869696</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,10 +886,121 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alexander Schäpers, Milad Avalinejad Bandari</t>
+          <t>Milad Avalinejad Bandari, Julia Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>C250246 Ljusdal NVI 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132325803</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hennan, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>529818</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6870044</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari, Alexander Schäpers</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>C250246 Ljusdal NVI 2025</t>
         </is>

--- a/artfynd/A 59078-2025 artfynd.xlsx
+++ b/artfynd/A 59078-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>C250246 Ljusdal NVI 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132325802</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>C250246 Ljusdal NVI 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132325751</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
           <t>C250246 Ljusdal NVI 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132325803</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>